--- a/docs/verification/files/rocscience/joints/rj016.xlsx
+++ b/docs/verification/files/rocscience/joints/rj016.xlsx
@@ -13830,17 +13830,9 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
-        <v>0.09</v>
-      </c>
-      <c r="B3" s="3">
-        <v>0.09</v>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
       <c r="E3" t="s">
         <v>221</v>
       </c>
@@ -13849,17 +13841,9 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
-        <v>0.45</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0.9</v>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
       <c r="E4" t="s">
         <v>223</v>
       </c>

--- a/docs/verification/files/rocscience/joints/rj016.xlsx
+++ b/docs/verification/files/rocscience/joints/rj016.xlsx
@@ -3374,7 +3374,9 @@
       <c r="G16" t="s">
         <v>34</v>
       </c>
-      <c r="D16"/>
+      <c r="D16">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>
